--- a/cve/oscommerce-cve.xlsx
+++ b/cve/oscommerce-cve.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,81 +462,81 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CVE-2002-1991</t>
+          <t>CVE-2006-6534</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>File Inclusion</t>
+          <t>XSS</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>['2.1']</t>
+          <t>['3.0']</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>['include_once.php']</t>
+          <t>['modules.php', 'customers.php', 'languages_definitions.php', 'products.php']</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['include_file']</t>
+          <t>['set', 'selected_box', 'lID', 'pID']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>PHP file inclusion vulnerability in osCommerce 2.1 execute arbitrary commands via the include_file parameter to include_once.php.</t>
+          <t>Multiple cross-site scripting (XSS) vulnerabilities in osCommerce 3.0a3 allow remote attackers to inject arbitrary web script or HTML via the (1) set parameter to admin/modules.php, the (2) selected_box parameter to definitiva/admin/customers.php, the (3) lID parameter to admin/languages_definitions.php, or the (4) pID parameter to admin/products.php.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVE-2002-2019</t>
+          <t>CVE-2008-0719</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>File Inclusion</t>
+          <t>SQL Injection</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>['2.1']</t>
+          <t>['3.1', '2.2']</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['include_once.php']</t>
+          <t>['customer_testimonials.php']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['include_file']</t>
+          <t>['testimonial_id']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>PHP remote file inclusion vulnerability in include_once.php in osCommerce (a.k.a. Exchange Project) 2.1 allows remote attackers to execute arbitrary PHP code via the include_file parameter.</t>
+          <t>SQL injection vulnerability in customer_testimonials.php in the Customer Testimonials 3 and 3.1 Addon for osCommerce Online Merchant 2.2 allows remote attackers to execute arbitrary SQL commands via the testimonial_id parameter.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVE-2003-1219</t>
+          <t>CVE-2012-1059</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -546,32 +546,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>['2.2']</t>
+          <t>['3.0.2']</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['html_output.php']</t>
+          <t>['main.php']</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>['osCsid']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cross-site scripting (XSS) vulnerability in the tep_href_link function in html_output.php for osCommerce before 2.2-MS3 allows remote attackers to inject arbitrary web script or HTML via the osCsid parameter.</t>
+          <t>Cross-site scripting (XSS) vulnerability in osCommerce/OM/Core/Site/Shop/Application/Cart/pages/main.php in OSCommerce Online Merchant 3.0.2 allows remote attackers to inject arbitrary web script or HTML via the value_title parameter, as demonstrated using the "Front" field in the shirt module.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVE-2005-0458</t>
+          <t>CVE-2012-1792</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -581,102 +581,102 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>['2.2']</t>
+          <t>['3.0.2']</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>['contact_us.php']</t>
+          <t>['DBCheck.php', 'index.php', 'index.php']</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>['enquiry']</t>
+          <t>['name']</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cross-site scripting (XSS) vulnerability in contact_us.php in osCommerce 2.2-MS2 allows remote attackers to inject arbitrary web script or HTML via the enquiry parameter.</t>
+          <t>Cross-site scripting (XSS) vulnerability in osCommerce/OM/Core/Site/Setup/Application/Install/RPC/DBCheck.php in OSCommerce Online Merchant 3.0.2, when the software is being installed, allows remote attackers to inject arbitrary web script or HTML via the name parameter to oscommerce/index.php, which is not properly handled in an error message.  NOTE: this might not be a vulnerability, since the ability to access oscommerce/index.php during installation may already imply administrator privileges.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVE-2005-4677</t>
+          <t>CVE-2012-2935</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SQL Injection</t>
+          <t>XSS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>['1.14']</t>
+          <t>['3.0.2']</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>['additional_images.php', 'product_info.php']</t>
+          <t>['main.php']</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>['products_id']</t>
+          <t>['title']</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SQL injection vulnerability in additional_images.php (aka the Additional Images module) before 1.14 in osCommerce allows remote attackers to execute arbitrary SQL commands via the products_id parameter to product_info.php.</t>
+          <t>Cross-site scripting (XSS) vulnerability in osCommerce/OM/Core/Site/Shop/Application/Checkout/pages/main.php in OSCommerce Online Merchant 3.0.2 allows remote attackers to inject arbitrary web script or HTML via the value_title parameter, a different vulnerability than CVE-2012-1059.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVE-2006-4297</t>
+          <t>CVE-2020-29070</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SQL Injection</t>
+          <t>XSS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>['2.2']</t>
+          <t>['2.3.4']</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>['shopping_cart.php']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>['array']</t>
+          <t>['title']</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>SQL injection vulnerability in shopping_cart.php in osCommerce before 2.2 Milestone 2 060817 allows remote attackers to execute arbitrary SQL commands via id array parameters.</t>
+          <t>osCommerce 2.3.4.1 has XSS vulnerability via the authenticated user entering the XSS payload into the title section of newsletters.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CVE-2006-5190</t>
+          <t>CVE-2022-35212</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -686,475 +686,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>['2.2']</t>
+          <t>['2.3.4']</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>['banner_manager.php', 'banner_statistics.php', 'countries.php', 'currencies.php', 'languages.php', 'manufacturers.php', 'newsletters.php', 'orders_status.php', 'products_attributes.php', 'products_expected.php', 'reviews.php', 'specials.php', 'stats_products_purchased.php', 'stats_products_viewed.php', 'tax_classes.php', 'tax_rates.php', 'zones.php', 'geo_zones.php']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>['page', 'zpage']</t>
+          <t>['tep_db_error']</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
-        <is>
-          <t>Multiple cross-site scripting (XSS) vulnerabilities in osCommerce 2.2 Milestone 2 Update 060817 allow remote attackers to inject arbitrary web script or HTML via the (1) page parameter in the (a) banner_manager.php, (b) banner_statistics.php, (c) countries.php, (d) currencies.php, (e) languages.php, (f) manufacturers.php, (g) newsletters.php, (h) orders_status.php, (i) products_attributes.php, (j) products_expected.php, (k) reviews.php, (l) specials.php, (m) stats_products_purchased.php, (n) stats_products_viewed.php, (o) tax_classes.php, (p) tax_rates.php, or (q) zones.php scripts in /admin, and the (2) zpage parameter in (r) admin/geo_zones.php.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CVE-2006-6534</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>XSS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>['3.0']</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>['modules.php', 'customers.php', 'languages_definitions.php', 'products.php']</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>['set', 'selected_box', 'lID', 'pID']</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Multiple cross-site scripting (XSS) vulnerabilities in osCommerce 3.0a3 allow remote attackers to inject arbitrary web script or HTML via the (1) set parameter to admin/modules.php, the (2) selected_box parameter to definitiva/admin/customers.php, the (3) lID parameter to admin/languages_definitions.php, or the (4) pID parameter to admin/products.php.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>CVE-2008-0719</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>SQL Injection</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>['3.1', '2.2']</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>['customer_testimonials.php']</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>['testimonial_id']</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>SQL injection vulnerability in customer_testimonials.php in the Customer Testimonials 3 and 3.1 Addon for osCommerce Online Merchant 2.2 allows remote attackers to execute arbitrary SQL commands via the testimonial_id parameter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>CVE-2008-4765</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>SQL Injection</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>['2.0']</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>['pollBooth.php']</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>['pollID']</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>SQL injection vulnerability in pollBooth.php in osCommerce Poll Booth Add-On 2.0 allows remote attackers to execute arbitrary SQL commands via the pollID parameter in a results operation.  NOTE: this issue was disclosed by an unreliable researcher, so it might be incorrect.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>CVE-2012-0311</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>XSS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>['2.2']</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Cross-site scripting (XSS) vulnerability in osCommerce 2.2MS1J before R9 allows remote attackers to inject arbitrary web script or HTML via unspecified vectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>CVE-2012-0312</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>XSS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>['2.3.1', '2.2']</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Cross-site scripting (XSS) vulnerability in osCommerce 2.2MS1J before R9, and osCommerce Online Merchant before 2.3.1, allows remote attackers to inject arbitrary web script or HTML via unspecified vectors.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>CVE-2012-1059</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>XSS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>['3.0.2']</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>['main.php']</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Cross-site scripting (XSS) vulnerability in osCommerce/OM/Core/Site/Shop/Application/Cart/pages/main.php in OSCommerce Online Merchant 3.0.2 allows remote attackers to inject arbitrary web script or HTML via the value_title parameter, as demonstrated using the "Front" field in the shirt module.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>CVE-2012-1792</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>XSS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>['3.0.2']</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>['DBCheck.php', 'index.php', 'index.php']</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>['name']</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Cross-site scripting (XSS) vulnerability in osCommerce/OM/Core/Site/Setup/Application/Install/RPC/DBCheck.php in OSCommerce Online Merchant 3.0.2, when the software is being installed, allows remote attackers to inject arbitrary web script or HTML via the name parameter to oscommerce/index.php, which is not properly handled in an error message.  NOTE: this might not be a vulnerability, since the ability to access oscommerce/index.php during installation may already imply administrator privileges.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>CVE-2014-10033</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>SQL Injection</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>['2.3.3']</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>['geo_zones.php']</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>['zID']</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>SQL injection vulnerability in the update_zone function in catalog/admin/geo_zones.php in osCommerce Online Merchant 2.3.3.4 and earlier allows remote administrators to execute arbitrary SQL commands via the zID parameter in a list action.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>CVE-2012-2935</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>XSS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>['3.0.2']</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>['main.php']</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Cross-site scripting (XSS) vulnerability in osCommerce/OM/Core/Site/Shop/Application/Checkout/pages/main.php in OSCommerce Online Merchant 3.0.2 allows remote attackers to inject arbitrary web script or HTML via the value_title parameter, a different vulnerability than CVE-2012-1059.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>CVE-2020-12058</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>XSS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>['1.0.6']</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>['order_status.php', 'tax_rates.php', 'languages.php', 'countries.php', 'tax_classes.php', 'reviews.php', 'zones.php', 'geo_zones.php']</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>['page', 'spage']</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Several XSS vulnerabilities in osCommerce CE Phoenix before 1.0.6.0 allow an attacker to inject and execute arbitrary JavaScript code. The malicious code can be injected as follows: the page parameter to catalog/admin/order_status.php, catalog/admin/tax_rates.php, catalog/admin/languages.php, catalog/admin/countries.php, catalog/admin/tax_classes.php, catalog/admin/reviews.php, or catalog/admin/zones.php; or the zpage or spage parameter to catalog/admin/geo_zones.php.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CVE-2020-27976</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Command Execution</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>['1.0.5']</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>['mail.php']</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>['POST']</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>osCommerce Phoenix CE before 1.0.5.4 allows OS command injection remotely. Within admin/mail.php, a from POST parameter can be passed to the application. This affects the PHP mail function, and the sendmail -f option.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>CVE-2020-29070</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>XSS</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>['2.3.4']</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>osCommerce 2.3.4.1 has XSS vulnerability via the authenticated user entering the XSS payload into the title section of newsletters.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>CVE-2022-35212</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>XSS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>['2.3.4']</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
         <is>
           <t>osCommerce2 before v2.3.4.1 was discovered to contain a cross-site scripting (XSS) vulnerability via the function tep_db_error().</t>
         </is>

--- a/cve/oscommerce-cve.xlsx
+++ b/cve/oscommerce-cve.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>['set', 'selected_box', 'lID', 'pID']</t>
+          <t>['lID', 'pID', 'selected_box', 'set']</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -497,46 +497,46 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVE-2008-0719</t>
+          <t>CVE-2012-1792</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SQL Injection</t>
+          <t>XSS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>['3.1', '2.2']</t>
+          <t>['3.0.2']</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>['customer_testimonials.php']</t>
+          <t>['DBCheck.php', 'index.php', 'index.php']</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>['testimonial_id']</t>
+          <t>['name']</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SQL injection vulnerability in customer_testimonials.php in the Customer Testimonials 3 and 3.1 Addon for osCommerce Online Merchant 2.2 allows remote attackers to execute arbitrary SQL commands via the testimonial_id parameter.</t>
+          <t>Cross-site scripting (XSS) vulnerability in osCommerce/OM/Core/Site/Setup/Application/Install/RPC/DBCheck.php in OSCommerce Online Merchant 3.0.2, when the software is being installed, allows remote attackers to inject arbitrary web script or HTML via the name parameter to oscommerce/index.php, which is not properly handled in an error message.  NOTE: this might not be a vulnerability, since the ability to access oscommerce/index.php during installation may already imply administrator privileges.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVE-2012-1059</t>
+          <t>CVE-2022-35212</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -546,160 +546,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>['3.0.2']</t>
+          <t>['2.3.4']</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>['main.php']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['tep_db_error']</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
-        <is>
-          <t>Cross-site scripting (XSS) vulnerability in osCommerce/OM/Core/Site/Shop/Application/Cart/pages/main.php in OSCommerce Online Merchant 3.0.2 allows remote attackers to inject arbitrary web script or HTML via the value_title parameter, as demonstrated using the "Front" field in the shirt module.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>CVE-2012-1792</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>XSS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>['3.0.2']</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>['DBCheck.php', 'index.php', 'index.php']</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>['name']</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Cross-site scripting (XSS) vulnerability in osCommerce/OM/Core/Site/Setup/Application/Install/RPC/DBCheck.php in OSCommerce Online Merchant 3.0.2, when the software is being installed, allows remote attackers to inject arbitrary web script or HTML via the name parameter to oscommerce/index.php, which is not properly handled in an error message.  NOTE: this might not be a vulnerability, since the ability to access oscommerce/index.php during installation may already imply administrator privileges.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>CVE-2012-2935</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>XSS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>['3.0.2']</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>['main.php']</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>['title']</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Cross-site scripting (XSS) vulnerability in osCommerce/OM/Core/Site/Shop/Application/Checkout/pages/main.php in OSCommerce Online Merchant 3.0.2 allows remote attackers to inject arbitrary web script or HTML via the value_title parameter, a different vulnerability than CVE-2012-1059.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>CVE-2020-29070</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>XSS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>['2.3.4']</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>['title']</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>osCommerce 2.3.4.1 has XSS vulnerability via the authenticated user entering the XSS payload into the title section of newsletters.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>CVE-2022-35212</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>XSS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>['2.3.4']</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>['tep_db_error']</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
         <is>
           <t>osCommerce2 before v2.3.4.1 was discovered to contain a cross-site scripting (XSS) vulnerability via the function tep_db_error().</t>
         </is>
